--- a/Work.xlsx
+++ b/Work.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding\print-hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E06344C-78D5-4E38-B6EB-55C7FB89721D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC483ED-E42E-43A9-B733-029795F44D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
   <si>
     <t>Date</t>
   </si>
@@ -421,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:F8"/>
+  <dimension ref="B2:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -472,7 +472,7 @@
         <v>8</v>
       </c>
       <c r="E4" s="2">
-        <f t="shared" ref="E4:E8" si="0">D4*2.5</f>
+        <f t="shared" ref="E4:E9" si="0">D4*2.5</f>
         <v>20</v>
       </c>
     </row>
@@ -490,6 +490,9 @@
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
+      <c r="F5" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
@@ -523,6 +526,9 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
+      <c r="F7" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="3">
@@ -532,11 +538,26 @@
         <v>9</v>
       </c>
       <c r="D8" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" s="2">
         <f t="shared" si="0"/>
-        <v>72.5</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="3">
+        <v>46050</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="2">
+        <v>31</v>
+      </c>
+      <c r="E9" s="2">
+        <f t="shared" si="0"/>
+        <v>77.5</v>
       </c>
     </row>
   </sheetData>

--- a/Work.xlsx
+++ b/Work.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding\print-hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC483ED-E42E-43A9-B733-029795F44D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3E197F-27E1-4666-B577-0A2C3DB3E1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
   <si>
     <t>Date</t>
   </si>
@@ -70,6 +70,12 @@
   </si>
   <si>
     <t>Paid</t>
+  </si>
+  <si>
+    <t>Haadiya</t>
+  </si>
+  <si>
+    <t>Sufiyaan</t>
   </si>
 </sst>
 </file>
@@ -126,19 +132,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -421,72 +436,77 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:F9"/>
+  <dimension ref="B2:F14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="5" width="16.7109375" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="16.7109375" style="7" customWidth="1"/>
+    <col min="3" max="5" width="16.7109375" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="3">
+      <c r="B3" s="6">
         <v>46048</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2">
-        <v>21</v>
-      </c>
-      <c r="E3" s="2">
+      <c r="D3" s="3">
+        <v>23</v>
+      </c>
+      <c r="E3" s="3">
         <f>D3*2.5</f>
-        <v>52.5</v>
+        <v>57.5</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="3">
+      <c r="B4" s="6">
         <v>46048</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3">
         <v>8</v>
       </c>
-      <c r="E4" s="2">
-        <f t="shared" ref="E4:E9" si="0">D4*2.5</f>
+      <c r="E4" s="3">
+        <f t="shared" ref="E4:E14" si="0">D4*2.5</f>
         <v>20</v>
       </c>
+      <c r="F4" s="3"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="3">
+      <c r="B5" s="6">
         <v>46048</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>34</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="3">
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
@@ -495,16 +515,16 @@
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="3">
+      <c r="B6" s="6">
         <v>46048</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>5</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="3">
         <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
@@ -513,16 +533,16 @@
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="3">
+      <c r="B7" s="6">
         <v>46049</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="3">
         <v>20</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="3">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
@@ -531,34 +551,126 @@
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="3">
+      <c r="B8" s="6">
         <v>46049</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="3">
         <v>30</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="3">
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
+      <c r="F8" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="3">
+      <c r="B9" s="6">
         <v>46050</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="3">
         <v>31</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="3">
         <f t="shared" si="0"/>
         <v>77.5</v>
       </c>
+      <c r="F9" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="6">
+        <v>46050</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="3">
+        <v>22</v>
+      </c>
+      <c r="E10" s="3">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="6">
+        <v>46050</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="3">
+        <v>12</v>
+      </c>
+      <c r="E11" s="3">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="6">
+        <v>46051</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="3">
+        <v>18</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="6">
+        <v>46051</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="3">
+        <v>14</v>
+      </c>
+      <c r="E13" s="3">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="6">
+        <v>46051</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="3">
+        <v>2</v>
+      </c>
+      <c r="E14" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F14" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Work.xlsx
+++ b/Work.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding\_print-hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{165B4CC6-6C08-41C5-AE23-200254D4646C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{109D3D17-67F3-45D9-9506-D1EE32F49795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="20">
   <si>
     <t>Date</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Yamin</t>
+  </si>
+  <si>
+    <t>with 20% off</t>
   </si>
 </sst>
 </file>
@@ -180,46 +183,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -526,36 +532,37 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="B1:J50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:J60"/>
+  <sheetFormatPr defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="12"/>
+    <col min="1" max="1" width="9.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="4"/>
+    <col min="8" max="8" width="19.85546875" style="4" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="5">
         <v>46048</v>
       </c>
@@ -566,18 +573,18 @@
         <v>23</v>
       </c>
       <c r="E3" s="8">
-        <f t="shared" ref="E3:E39" si="0">D3*2.5</f>
+        <f t="shared" ref="E3:E60" si="0">D3*2.5</f>
         <v>57.5</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="1">
-        <f>(SUM(D3:D38)*2.5)</f>
-        <v>1287.5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J3" s="10">
+        <f>(SUM(D3:D100)*2.5)</f>
+        <v>1987.5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="5">
         <v>46048</v>
       </c>
@@ -595,7 +602,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>46048</v>
       </c>
@@ -613,7 +620,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="5">
         <v>46048</v>
       </c>
@@ -631,7 +638,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>46049</v>
       </c>
@@ -649,7 +656,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="5">
         <v>46049</v>
       </c>
@@ -667,7 +674,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>46050</v>
       </c>
@@ -685,7 +692,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="5">
         <v>46050</v>
       </c>
@@ -703,7 +710,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <v>46050</v>
       </c>
@@ -721,7 +728,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
         <v>46051</v>
       </c>
@@ -739,7 +746,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>46051</v>
       </c>
@@ -757,7 +764,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
         <v>46051</v>
       </c>
@@ -771,11 +778,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="11" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="5">
         <v>46054</v>
       </c>
@@ -793,7 +800,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="5">
         <v>46055</v>
       </c>
@@ -811,7 +818,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="5">
         <v>46055</v>
       </c>
@@ -829,7 +836,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="5">
         <v>46055</v>
       </c>
@@ -847,7 +854,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="5">
         <v>46055</v>
       </c>
@@ -865,7 +872,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="5">
         <v>46056</v>
       </c>
@@ -883,7 +890,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="5">
         <v>46056</v>
       </c>
@@ -901,7 +908,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="5">
         <v>46058</v>
       </c>
@@ -919,7 +926,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="5">
         <v>46058</v>
       </c>
@@ -937,7 +944,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="5">
         <v>46058</v>
       </c>
@@ -955,8 +962,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="13">
+    <row r="25" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="12">
         <v>46062</v>
       </c>
       <c r="C25" s="6" t="s">
@@ -973,14 +980,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="13">
+    <row r="26" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="12">
         <v>46062</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" s="10">
         <v>9</v>
       </c>
       <c r="E26" s="7">
@@ -991,14 +998,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="13">
+    <row r="27" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="12">
         <v>46062</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27" s="10">
         <v>19</v>
       </c>
       <c r="E27" s="7">
@@ -1009,14 +1016,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="13">
+    <row r="28" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="12">
         <v>46063</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28" s="10">
         <v>11</v>
       </c>
       <c r="E28" s="7">
@@ -1027,14 +1034,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="13">
+    <row r="29" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="12">
         <v>46064</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D29" s="10">
         <v>5</v>
       </c>
       <c r="E29" s="7">
@@ -1045,14 +1052,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="13">
+    <row r="30" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="12">
         <v>46064</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D30" s="10">
         <v>5</v>
       </c>
       <c r="E30" s="7">
@@ -1063,14 +1070,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="13">
+    <row r="31" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="12">
         <v>46065</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D31" s="10">
         <v>12</v>
       </c>
       <c r="E31" s="7">
@@ -1081,14 +1088,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="13">
+    <row r="32" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="12">
         <v>46065</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D32" s="10">
         <v>10</v>
       </c>
       <c r="E32" s="7">
@@ -1099,14 +1106,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="13">
+    <row r="33" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="12">
         <v>46065</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D33" s="10">
         <v>18</v>
       </c>
       <c r="E33" s="7">
@@ -1117,14 +1124,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="13">
+    <row r="34" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="12">
         <v>46073</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D34" s="10">
         <v>12</v>
       </c>
       <c r="E34" s="7">
@@ -1135,128 +1142,564 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="13">
+    <row r="35" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="12">
         <v>46073</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D35" s="10">
         <v>34</v>
       </c>
       <c r="E35" s="7">
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
-      <c r="F35" s="10" t="s">
+      <c r="F35" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="12">
+        <v>46073</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" s="10">
+        <v>5</v>
+      </c>
+      <c r="E36" s="7">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="12">
+        <v>46073</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="10">
+        <v>28</v>
+      </c>
+      <c r="E37" s="7">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="12">
+        <v>46075</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="10">
+        <v>12</v>
+      </c>
+      <c r="E38" s="7">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H38" s="14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="12">
+        <v>46075</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" s="10">
+        <v>6</v>
+      </c>
+      <c r="E39" s="7">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F39" s="11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="36" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="13">
-        <v>46073</v>
-      </c>
-      <c r="C36" s="12" t="s">
+      <c r="H39" s="4">
+        <f>D39*2.5*0.8</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="12">
+        <v>46075</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D40" s="10">
+        <v>11</v>
+      </c>
+      <c r="E40" s="7">
+        <f t="shared" si="0"/>
+        <v>27.5</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H40" s="4">
+        <f t="shared" ref="H40:H60" si="1">D40*2.5*0.8</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="12">
+        <v>46078</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="10">
+        <v>10</v>
+      </c>
+      <c r="E41" s="7">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H41" s="4">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="12">
+        <v>46078</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="10">
+        <v>3</v>
+      </c>
+      <c r="E42" s="7">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H42" s="4">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="12">
+        <v>46078</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E36" s="7">
+      <c r="D43" s="10">
+        <v>4</v>
+      </c>
+      <c r="E43" s="7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H43" s="4">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="12">
+        <v>46079</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="10">
+        <v>4</v>
+      </c>
+      <c r="E44" s="7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H44" s="4">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="12">
+        <v>46082</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45" s="10">
+        <v>16</v>
+      </c>
+      <c r="E45" s="7">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H45" s="4">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="12">
+        <v>46082</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="10">
+        <v>23</v>
+      </c>
+      <c r="E46" s="7">
+        <f t="shared" si="0"/>
+        <v>57.5</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H46" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="12">
+        <v>46082</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" s="10">
+        <v>39</v>
+      </c>
+      <c r="E47" s="7">
+        <f t="shared" si="0"/>
+        <v>97.5</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H47" s="4">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="12">
+        <v>46082</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48" s="10">
+        <v>11</v>
+      </c>
+      <c r="E48" s="7">
+        <f t="shared" si="0"/>
+        <v>27.5</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H48" s="4">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="12">
+        <v>46086</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="10">
+        <v>12</v>
+      </c>
+      <c r="E49" s="7">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H49" s="4">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="12">
+        <v>46086</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="10">
+        <v>9</v>
+      </c>
+      <c r="E50" s="7">
+        <f t="shared" si="0"/>
+        <v>22.5</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H50" s="4">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="12">
+        <v>46086</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" s="10">
+        <v>32</v>
+      </c>
+      <c r="E51" s="7">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H51" s="4">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="12">
+        <v>46086</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" s="10">
+        <v>15</v>
+      </c>
+      <c r="E52" s="7">
+        <f t="shared" si="0"/>
+        <v>37.5</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H52" s="4">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="12">
+        <v>46086</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D53" s="10">
+        <v>12</v>
+      </c>
+      <c r="E53" s="7">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H53" s="4">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="12">
+        <v>46086</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="10">
+        <v>6</v>
+      </c>
+      <c r="E54" s="7">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H54" s="4">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="12">
+        <v>46087</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="10">
+        <v>16</v>
+      </c>
+      <c r="E55" s="7">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H55" s="4">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="12">
+        <v>46089</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" s="10">
+        <v>17</v>
+      </c>
+      <c r="E56" s="7">
+        <f t="shared" si="0"/>
+        <v>42.5</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H56" s="4">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="12">
+        <v>46089</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="10">
+        <v>5</v>
+      </c>
+      <c r="E57" s="7">
         <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
-      <c r="F36" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="13">
-        <v>46073</v>
-      </c>
-      <c r="C37" s="12" t="s">
+      <c r="F57" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H57" s="4">
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="D37" s="1">
-        <v>28</v>
-      </c>
-      <c r="E37" s="7">
-        <f t="shared" si="0"/>
-        <v>70</v>
-      </c>
-      <c r="F37" s="10" t="s">
+    </row>
+    <row r="58" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="12">
+        <v>46092</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" s="10">
+        <v>10</v>
+      </c>
+      <c r="E58" s="7">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="F58" s="11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="38" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="13">
-        <v>46075</v>
-      </c>
-      <c r="C38" s="12" t="s">
+      <c r="H58" s="4">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="12">
+        <v>46092</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="1">
-        <v>12</v>
-      </c>
-      <c r="E38" s="7">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="F38" s="10" t="s">
+      <c r="D59" s="10">
+        <v>10</v>
+      </c>
+      <c r="E59" s="7">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="F59" s="11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="39" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="13">
-        <v>46075</v>
-      </c>
-      <c r="C39" s="12" t="s">
+      <c r="H59" s="4">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="12">
+        <v>46092</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" s="10">
+        <v>9</v>
+      </c>
+      <c r="E60" s="10">
+        <f t="shared" si="0"/>
+        <v>22.5</v>
+      </c>
+      <c r="F60" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H60" s="4">
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="D39" s="1">
-        <v>6</v>
-      </c>
-      <c r="E39" s="7">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="F39" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E40" s="7"/>
-    </row>
-    <row r="41" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E41" s="7"/>
-    </row>
-    <row r="42" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E42" s="7"/>
-    </row>
-    <row r="43" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E43" s="7"/>
-    </row>
-    <row r="44" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E44" s="7"/>
-    </row>
-    <row r="45" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E45" s="7"/>
-    </row>
-    <row r="46" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E46" s="7"/>
-    </row>
-    <row r="47" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E47" s="7"/>
-    </row>
-    <row r="48" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E48" s="7"/>
-    </row>
-    <row r="49" spans="5:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E49" s="7"/>
-    </row>
-    <row r="50" spans="5:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E50" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Work.xlsx
+++ b/Work.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding\_print-hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{109D3D17-67F3-45D9-9506-D1EE32F49795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122BFF97-79D5-446D-BEC7-7C0E9FDE9B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="19">
   <si>
     <t>Date</t>
   </si>
@@ -91,9 +91,6 @@
   </si>
   <si>
     <t>Yamin</t>
-  </si>
-  <si>
-    <t>with 20% off</t>
   </si>
 </sst>
 </file>
@@ -183,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -222,9 +219,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -532,7 +526,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="B2:J60"/>
+  <dimension ref="B2:I69"/>
   <sheetFormatPr defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" bestFit="1" customWidth="1"/>
@@ -540,12 +534,10 @@
     <col min="3" max="3" width="16.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="16.7109375" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="4"/>
-    <col min="8" max="8" width="19.85546875" style="4" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="4"/>
+    <col min="7" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -562,7 +554,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="5">
         <v>46048</v>
       </c>
@@ -573,18 +565,18 @@
         <v>23</v>
       </c>
       <c r="E3" s="8">
-        <f t="shared" ref="E3:E60" si="0">D3*2.5</f>
+        <f t="shared" ref="E3:E69" si="0">D3*2.5</f>
         <v>57.5</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="10">
+      <c r="I3" s="10">
         <f>(SUM(D3:D100)*2.5)</f>
-        <v>1987.5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="5">
         <v>46048</v>
       </c>
@@ -602,7 +594,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>46048</v>
       </c>
@@ -620,7 +612,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="5">
         <v>46048</v>
       </c>
@@ -638,7 +630,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>46049</v>
       </c>
@@ -656,7 +648,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="5">
         <v>46049</v>
       </c>
@@ -674,7 +666,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>46050</v>
       </c>
@@ -692,7 +684,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="5">
         <v>46050</v>
       </c>
@@ -710,7 +702,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <v>46050</v>
       </c>
@@ -728,7 +720,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
         <v>46051</v>
       </c>
@@ -746,7 +738,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>46051</v>
       </c>
@@ -764,7 +756,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
         <v>46051</v>
       </c>
@@ -782,7 +774,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="5">
         <v>46054</v>
       </c>
@@ -800,7 +792,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="2:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="5">
         <v>46055</v>
       </c>
@@ -1106,7 +1098,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="12">
         <v>46065</v>
       </c>
@@ -1124,7 +1116,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="12">
         <v>46073</v>
       </c>
@@ -1142,7 +1134,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="12">
         <v>46073</v>
       </c>
@@ -1160,7 +1152,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="12">
         <v>46073</v>
       </c>
@@ -1178,7 +1170,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="12">
         <v>46073</v>
       </c>
@@ -1196,7 +1188,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="12">
         <v>46075</v>
       </c>
@@ -1213,11 +1205,8 @@
       <c r="F38" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H38" s="14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="12">
         <v>46075</v>
       </c>
@@ -1234,12 +1223,8 @@
       <c r="F39" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H39" s="4">
-        <f>D39*2.5*0.8</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="12">
         <v>46075</v>
       </c>
@@ -1256,12 +1241,8 @@
       <c r="F40" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H40" s="4">
-        <f t="shared" ref="H40:H60" si="1">D40*2.5*0.8</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="12">
         <v>46078</v>
       </c>
@@ -1278,12 +1259,8 @@
       <c r="F41" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H41" s="4">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="12">
         <v>46078</v>
       </c>
@@ -1300,12 +1277,8 @@
       <c r="F42" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H42" s="4">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="12">
         <v>46078</v>
       </c>
@@ -1322,12 +1295,8 @@
       <c r="F43" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H43" s="4">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="12">
         <v>46079</v>
       </c>
@@ -1344,12 +1313,8 @@
       <c r="F44" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H44" s="4">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="12">
         <v>46082</v>
       </c>
@@ -1366,12 +1331,8 @@
       <c r="F45" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H45" s="4">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="12">
         <v>46082</v>
       </c>
@@ -1388,12 +1349,8 @@
       <c r="F46" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H46" s="4">
-        <f t="shared" si="1"/>
-        <v>46</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="12">
         <v>46082</v>
       </c>
@@ -1410,12 +1367,8 @@
       <c r="F47" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H47" s="4">
-        <f t="shared" si="1"/>
-        <v>78</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="12">
         <v>46082</v>
       </c>
@@ -1432,12 +1385,8 @@
       <c r="F48" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H48" s="4">
-        <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="12">
         <v>46086</v>
       </c>
@@ -1454,12 +1403,8 @@
       <c r="F49" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H49" s="4">
-        <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="12">
         <v>46086</v>
       </c>
@@ -1476,12 +1421,8 @@
       <c r="F50" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H50" s="4">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="12">
         <v>46086</v>
       </c>
@@ -1498,12 +1439,8 @@
       <c r="F51" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H51" s="4">
-        <f t="shared" si="1"/>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="12">
         <v>46086</v>
       </c>
@@ -1520,12 +1457,8 @@
       <c r="F52" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H52" s="4">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="12">
         <v>46086</v>
       </c>
@@ -1539,15 +1472,11 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="F53" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H53" s="4">
-        <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F53" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="12">
         <v>46086</v>
       </c>
@@ -1564,12 +1493,8 @@
       <c r="F54" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H54" s="4">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="12">
         <v>46087</v>
       </c>
@@ -1586,12 +1511,8 @@
       <c r="F55" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H55" s="4">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="12">
         <v>46089</v>
       </c>
@@ -1608,12 +1529,8 @@
       <c r="F56" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H56" s="4">
-        <f t="shared" si="1"/>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="12">
         <v>46089</v>
       </c>
@@ -1630,12 +1547,8 @@
       <c r="F57" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H57" s="4">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="12">
         <v>46092</v>
       </c>
@@ -1652,12 +1565,8 @@
       <c r="F58" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H58" s="4">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="12">
         <v>46092</v>
       </c>
@@ -1671,15 +1580,11 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="F59" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H59" s="4">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F59" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="12">
         <v>46092</v>
       </c>
@@ -1687,18 +1592,176 @@
         <v>5</v>
       </c>
       <c r="D60" s="10">
+        <v>19</v>
+      </c>
+      <c r="E60" s="10">
+        <f t="shared" si="0"/>
+        <v>47.5</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="12">
+        <v>46092</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E60" s="10">
-        <f t="shared" si="0"/>
-        <v>22.5</v>
-      </c>
-      <c r="F60" s="11" t="s">
+      <c r="D61" s="10">
+        <v>11</v>
+      </c>
+      <c r="E61" s="10">
+        <f t="shared" si="0"/>
+        <v>27.5</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="12">
+        <v>46092</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" s="10">
+        <v>8</v>
+      </c>
+      <c r="E62" s="10">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="F62" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H60" s="4">
-        <f t="shared" si="1"/>
+    </row>
+    <row r="63" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="12">
+        <v>46092</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D63" s="10">
+        <v>46</v>
+      </c>
+      <c r="E63" s="10">
+        <f t="shared" si="0"/>
+        <v>115</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="12">
+        <v>46096</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D64" s="10">
+        <v>17</v>
+      </c>
+      <c r="E64" s="10">
+        <f t="shared" si="0"/>
+        <v>42.5</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="12">
+        <v>46104</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" s="10">
+        <v>15</v>
+      </c>
+      <c r="E65" s="10">
+        <f t="shared" si="0"/>
+        <v>37.5</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="12">
+        <v>46104</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" s="10">
+        <v>36</v>
+      </c>
+      <c r="E66" s="10">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="12">
+        <v>46104</v>
+      </c>
+      <c r="C67" s="4" t="s">
         <v>18</v>
+      </c>
+      <c r="D67" s="10">
+        <v>4</v>
+      </c>
+      <c r="E67" s="10">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="F67" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="12">
+        <v>46105</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D68" s="10">
+        <v>16</v>
+      </c>
+      <c r="E68" s="10">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="F68" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="12">
+        <v>46105</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D69" s="10">
+        <v>6</v>
+      </c>
+      <c r="E69" s="10">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F69" s="11" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Work.xlsx
+++ b/Work.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding\_print-hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122BFF97-79D5-446D-BEC7-7C0E9FDE9B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3083393D-4B31-4B64-A331-CD46BD9EAC1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="27">
   <si>
     <t>Date</t>
   </si>
@@ -91,6 +91,30 @@
   </si>
   <si>
     <t>Yamin</t>
+  </si>
+  <si>
+    <t>Alisha</t>
+  </si>
+  <si>
+    <t>Sameer</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Binding</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Ariz</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Yusuf</t>
   </si>
 </sst>
 </file>
@@ -526,10 +550,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="B2:I69"/>
+  <dimension ref="B1:I129"/>
   <sheetFormatPr defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="16.7109375" style="10" bestFit="1" customWidth="1"/>
@@ -537,6 +561,7 @@
     <col min="7" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -552,6 +577,16 @@
       </c>
       <c r="F2" s="2" t="s">
         <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="10">
+        <f>SUM(E3:E1000)*0.9</f>
+        <v>5447.25</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -565,15 +600,14 @@
         <v>23</v>
       </c>
       <c r="E3" s="8">
-        <f t="shared" ref="E3:E69" si="0">D3*2.5</f>
+        <f t="shared" ref="E3:E79" si="0">D3*2.5</f>
         <v>57.5</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="10">
-        <f>(SUM(D3:D100)*2.5)</f>
-        <v>2410</v>
+      <c r="G3" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -593,6 +627,9 @@
       <c r="F4" s="9" t="s">
         <v>6</v>
       </c>
+      <c r="G4" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="5" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
@@ -611,6 +648,9 @@
       <c r="F5" s="9" t="s">
         <v>6</v>
       </c>
+      <c r="G5" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="6" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="5">
@@ -629,6 +669,9 @@
       <c r="F6" s="9" t="s">
         <v>6</v>
       </c>
+      <c r="G6" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="7" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
@@ -647,6 +690,9 @@
       <c r="F7" s="9" t="s">
         <v>6</v>
       </c>
+      <c r="G7" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="8" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="5">
@@ -665,6 +711,9 @@
       <c r="F8" s="9" t="s">
         <v>6</v>
       </c>
+      <c r="G8" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="9" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
@@ -683,6 +732,9 @@
       <c r="F9" s="9" t="s">
         <v>6</v>
       </c>
+      <c r="G9" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="10" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="5">
@@ -701,6 +753,9 @@
       <c r="F10" s="9" t="s">
         <v>6</v>
       </c>
+      <c r="G10" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="11" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
@@ -719,6 +774,9 @@
       <c r="F11" s="9" t="s">
         <v>6</v>
       </c>
+      <c r="G11" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="12" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
@@ -737,6 +795,9 @@
       <c r="F12" s="9" t="s">
         <v>6</v>
       </c>
+      <c r="G12" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="13" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
@@ -755,6 +816,9 @@
       <c r="F13" s="9" t="s">
         <v>6</v>
       </c>
+      <c r="G13" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="14" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
@@ -773,6 +837,9 @@
       <c r="F14" s="11" t="s">
         <v>14</v>
       </c>
+      <c r="G14" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="15" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="5">
@@ -791,6 +858,9 @@
       <c r="F15" s="9" t="s">
         <v>6</v>
       </c>
+      <c r="G15" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="16" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="5">
@@ -809,8 +879,11 @@
       <c r="F16" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G16" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="5">
         <v>46055</v>
       </c>
@@ -827,8 +900,11 @@
       <c r="F17" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="18" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G17" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="5">
         <v>46055</v>
       </c>
@@ -845,8 +921,11 @@
       <c r="F18" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G18" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="5">
         <v>46055</v>
       </c>
@@ -863,8 +942,11 @@
       <c r="F19" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="20" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G19" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="5">
         <v>46056</v>
       </c>
@@ -881,8 +963,11 @@
       <c r="F20" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="21" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G20" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="5">
         <v>46056</v>
       </c>
@@ -899,8 +984,11 @@
       <c r="F21" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G21" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="5">
         <v>46058</v>
       </c>
@@ -917,8 +1005,11 @@
       <c r="F22" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="23" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G22" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="5">
         <v>46058</v>
       </c>
@@ -935,8 +1026,11 @@
       <c r="F23" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="24" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G23" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="5">
         <v>46058</v>
       </c>
@@ -953,8 +1047,11 @@
       <c r="F24" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="25" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G24" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="12">
         <v>46062</v>
       </c>
@@ -971,8 +1068,11 @@
       <c r="F25" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="26" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G25" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="12">
         <v>46062</v>
       </c>
@@ -989,8 +1089,11 @@
       <c r="F26" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="27" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G26" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="12">
         <v>46062</v>
       </c>
@@ -1007,8 +1110,11 @@
       <c r="F27" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G27" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="12">
         <v>46063</v>
       </c>
@@ -1025,8 +1131,11 @@
       <c r="F28" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G28" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="12">
         <v>46064</v>
       </c>
@@ -1043,8 +1152,11 @@
       <c r="F29" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="30" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G29" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="12">
         <v>46064</v>
       </c>
@@ -1061,8 +1173,11 @@
       <c r="F30" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="31" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G30" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="12">
         <v>46065</v>
       </c>
@@ -1079,8 +1194,11 @@
       <c r="F31" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="32" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G31" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="12">
         <v>46065</v>
       </c>
@@ -1097,8 +1215,11 @@
       <c r="F32" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="33" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G32" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="12">
         <v>46065</v>
       </c>
@@ -1115,8 +1236,11 @@
       <c r="F33" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="34" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G33" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="12">
         <v>46073</v>
       </c>
@@ -1133,8 +1257,11 @@
       <c r="F34" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="35" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G34" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="12">
         <v>46073</v>
       </c>
@@ -1151,8 +1278,11 @@
       <c r="F35" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="36" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G35" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="12">
         <v>46073</v>
       </c>
@@ -1169,8 +1299,11 @@
       <c r="F36" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="37" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G36" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="12">
         <v>46073</v>
       </c>
@@ -1187,8 +1320,11 @@
       <c r="F37" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="38" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G37" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="12">
         <v>46075</v>
       </c>
@@ -1205,8 +1341,11 @@
       <c r="F38" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="39" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G38" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="12">
         <v>46075</v>
       </c>
@@ -1223,8 +1362,11 @@
       <c r="F39" s="11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="40" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G39" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="12">
         <v>46075</v>
       </c>
@@ -1241,8 +1383,11 @@
       <c r="F40" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="41" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G40" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="12">
         <v>46078</v>
       </c>
@@ -1259,8 +1404,11 @@
       <c r="F41" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="42" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G41" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="12">
         <v>46078</v>
       </c>
@@ -1277,8 +1425,11 @@
       <c r="F42" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="43" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G42" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="12">
         <v>46078</v>
       </c>
@@ -1295,8 +1446,11 @@
       <c r="F43" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="44" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G43" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="12">
         <v>46079</v>
       </c>
@@ -1313,8 +1467,11 @@
       <c r="F44" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="45" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G44" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="12">
         <v>46082</v>
       </c>
@@ -1331,8 +1488,11 @@
       <c r="F45" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="46" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G45" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="12">
         <v>46082</v>
       </c>
@@ -1349,8 +1509,11 @@
       <c r="F46" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="47" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G46" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="12">
         <v>46082</v>
       </c>
@@ -1367,8 +1530,11 @@
       <c r="F47" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="48" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G47" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="12">
         <v>46082</v>
       </c>
@@ -1385,8 +1551,11 @@
       <c r="F48" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="49" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G48" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="12">
         <v>46086</v>
       </c>
@@ -1403,8 +1572,11 @@
       <c r="F49" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="50" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G49" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="12">
         <v>46086</v>
       </c>
@@ -1421,8 +1593,11 @@
       <c r="F50" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="51" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G50" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="12">
         <v>46086</v>
       </c>
@@ -1439,8 +1614,11 @@
       <c r="F51" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="52" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G51" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="12">
         <v>46086</v>
       </c>
@@ -1457,8 +1635,11 @@
       <c r="F52" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="53" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G52" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="12">
         <v>46086</v>
       </c>
@@ -1475,8 +1656,11 @@
       <c r="F53" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="54" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G53" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="12">
         <v>46086</v>
       </c>
@@ -1493,8 +1677,11 @@
       <c r="F54" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="55" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G54" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="12">
         <v>46087</v>
       </c>
@@ -1511,8 +1698,11 @@
       <c r="F55" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="56" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G55" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="12">
         <v>46089</v>
       </c>
@@ -1529,8 +1719,11 @@
       <c r="F56" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="57" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G56" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="12">
         <v>46089</v>
       </c>
@@ -1547,8 +1740,11 @@
       <c r="F57" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="58" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G57" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="12">
         <v>46092</v>
       </c>
@@ -1562,11 +1758,14 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="F58" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="59" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F58" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="12">
         <v>46092</v>
       </c>
@@ -1583,8 +1782,11 @@
       <c r="F59" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="60" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G59" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="12">
         <v>46092</v>
       </c>
@@ -1601,8 +1803,11 @@
       <c r="F60" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="61" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G60" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="12">
         <v>46092</v>
       </c>
@@ -1619,8 +1824,11 @@
       <c r="F61" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="62" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G61" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="12">
         <v>46092</v>
       </c>
@@ -1634,11 +1842,14 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="F62" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="63" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F62" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="12">
         <v>46092</v>
       </c>
@@ -1655,8 +1866,11 @@
       <c r="F63" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="64" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G63" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="12">
         <v>46096</v>
       </c>
@@ -1670,11 +1884,14 @@
         <f t="shared" si="0"/>
         <v>42.5</v>
       </c>
-      <c r="F64" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="65" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F64" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="12">
         <v>46104</v>
       </c>
@@ -1688,11 +1905,14 @@
         <f t="shared" si="0"/>
         <v>37.5</v>
       </c>
-      <c r="F65" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F65" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="12">
         <v>46104</v>
       </c>
@@ -1709,8 +1929,11 @@
       <c r="F66" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="67" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G66" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="12">
         <v>46104</v>
       </c>
@@ -1724,11 +1947,14 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="F67" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="68" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F67" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="12">
         <v>46105</v>
       </c>
@@ -1742,11 +1968,14 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="F68" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="69" spans="2:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F68" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="12">
         <v>46105</v>
       </c>
@@ -1760,8 +1989,803 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="F69" s="11" t="s">
+      <c r="F69" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="12">
+        <v>46125</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70" s="10">
+        <v>15</v>
+      </c>
+      <c r="E70" s="10">
+        <f t="shared" si="0"/>
+        <v>37.5</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="12">
+        <v>46125</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D71" s="10">
+        <v>35</v>
+      </c>
+      <c r="E71" s="10">
+        <f t="shared" si="0"/>
+        <v>87.5</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="12">
+        <v>46126</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72" s="10">
+        <v>50</v>
+      </c>
+      <c r="E72" s="10">
+        <f t="shared" si="0"/>
+        <v>125</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="12">
+        <v>46126</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D73" s="10">
+        <v>51</v>
+      </c>
+      <c r="E73" s="10">
+        <f t="shared" si="0"/>
+        <v>127.5</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="74" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="12">
+        <v>46126</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D74" s="10">
+        <v>6</v>
+      </c>
+      <c r="E74" s="10">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="75" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="12">
+        <v>46127</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" s="10">
+        <v>120</v>
+      </c>
+      <c r="E75" s="10">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B76" s="12">
+        <v>46127</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D76" s="10">
+        <v>23</v>
+      </c>
+      <c r="E76" s="10">
+        <f t="shared" si="0"/>
+        <v>57.5</v>
+      </c>
+      <c r="F76" s="11" t="s">
         <v>14</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="77" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B77" s="12">
+        <v>46128</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D77" s="10">
+        <v>21</v>
+      </c>
+      <c r="E77" s="10">
+        <f t="shared" si="0"/>
+        <v>52.5</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B78" s="12">
+        <v>46128</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" s="10">
+        <v>15</v>
+      </c>
+      <c r="E78" s="10">
+        <f t="shared" si="0"/>
+        <v>37.5</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="79" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="12">
+        <v>46129</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79" s="10">
+        <v>118</v>
+      </c>
+      <c r="E79" s="10">
+        <f t="shared" si="0"/>
+        <v>295</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="12">
+        <v>46129</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D80" s="10">
+        <v>86</v>
+      </c>
+      <c r="E80" s="10">
+        <f t="shared" ref="E80:E129" si="1">D80*2.5</f>
+        <v>215</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="81" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="12">
+        <v>46129</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="10">
+        <v>149</v>
+      </c>
+      <c r="E81" s="10">
+        <f t="shared" si="1"/>
+        <v>372.5</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="12">
+        <v>46129</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D82" s="10">
+        <v>49</v>
+      </c>
+      <c r="E82" s="10">
+        <f t="shared" si="1"/>
+        <v>122.5</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="12">
+        <v>46130</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D83" s="10">
+        <v>31</v>
+      </c>
+      <c r="E83" s="10">
+        <f t="shared" si="1"/>
+        <v>77.5</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="12">
+        <v>46130</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="10">
+        <v>58</v>
+      </c>
+      <c r="E84" s="10">
+        <f t="shared" si="1"/>
+        <v>145</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="12">
+        <v>46130</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D85" s="10">
+        <v>10</v>
+      </c>
+      <c r="E85" s="10">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="12">
+        <v>46130</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D86" s="10">
+        <v>350</v>
+      </c>
+      <c r="E86" s="10">
+        <f t="shared" si="1"/>
+        <v>875</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="12">
+        <v>46131</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D87" s="10">
+        <v>4</v>
+      </c>
+      <c r="E87" s="10">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B88" s="12">
+        <v>46131</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" s="10">
+        <v>15</v>
+      </c>
+      <c r="E88" s="10">
+        <f t="shared" si="1"/>
+        <v>37.5</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B89" s="12">
+        <v>46131</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D89" s="10">
+        <v>49</v>
+      </c>
+      <c r="E89" s="10">
+        <f t="shared" si="1"/>
+        <v>122.5</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="90" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B90" s="12">
+        <v>46132</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90" s="10">
+        <v>14</v>
+      </c>
+      <c r="E90" s="10">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="F90" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B91" s="12">
+        <v>46132</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D91" s="10">
+        <v>7</v>
+      </c>
+      <c r="E91" s="10">
+        <f t="shared" si="1"/>
+        <v>17.5</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="92" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B92" s="12">
+        <v>46132</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D92" s="10">
+        <v>10</v>
+      </c>
+      <c r="E92" s="10">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="F92" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="12">
+        <v>46132</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D93" s="10">
+        <v>2</v>
+      </c>
+      <c r="E93" s="10">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="F93" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B94" s="12">
+        <v>46133</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D94" s="10">
+        <v>27</v>
+      </c>
+      <c r="E94" s="10">
+        <v>125</v>
+      </c>
+      <c r="F94" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="95" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B95" s="12">
+        <v>46133</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D95" s="10">
+        <v>27</v>
+      </c>
+      <c r="E95" s="10">
+        <v>130</v>
+      </c>
+      <c r="F95" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="96" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B96" s="12">
+        <v>46133</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D96" s="10">
+        <v>20</v>
+      </c>
+      <c r="E96" s="10">
+        <v>135</v>
+      </c>
+      <c r="F96" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="12">
+        <v>46133</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D97" s="10">
+        <v>6</v>
+      </c>
+      <c r="E97" s="10">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B98" s="12">
+        <v>46133</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D98" s="10">
+        <v>7</v>
+      </c>
+      <c r="E98" s="10">
+        <f t="shared" si="1"/>
+        <v>17.5</v>
+      </c>
+      <c r="F98" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E99" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E100" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E101" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E102" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E103" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E104" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E105" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E106" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E107" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E108" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E109" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E110" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E111" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E112" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E113" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E114" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E115" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E116" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E117" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E118" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E119" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E120" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E121" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E122" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E123" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E124" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E125" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E126" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E127" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E128" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E129" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Work.xlsx
+++ b/Work.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding\_print-hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3083393D-4B31-4B64-A331-CD46BD9EAC1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13BAA03E-BAF5-4965-80ED-AF0017BC9753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2136,8 +2136,8 @@
         <f t="shared" si="0"/>
         <v>57.5</v>
       </c>
-      <c r="F76" s="11" t="s">
-        <v>14</v>
+      <c r="F76" s="9" t="s">
+        <v>6</v>
       </c>
       <c r="G76" s="4" t="s">
         <v>23</v>
@@ -2430,8 +2430,8 @@
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="F90" s="11" t="s">
-        <v>14</v>
+      <c r="F90" s="9" t="s">
+        <v>6</v>
       </c>
       <c r="G90" s="4" t="s">
         <v>23</v>
@@ -2472,8 +2472,8 @@
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="F92" s="11" t="s">
-        <v>14</v>
+      <c r="F92" s="9" t="s">
+        <v>6</v>
       </c>
       <c r="G92" s="4" t="s">
         <v>23</v>
@@ -2513,8 +2513,8 @@
       <c r="E94" s="10">
         <v>125</v>
       </c>
-      <c r="F94" s="11" t="s">
-        <v>14</v>
+      <c r="F94" s="9" t="s">
+        <v>6</v>
       </c>
       <c r="G94" s="4" t="s">
         <v>21</v>
@@ -2553,8 +2553,8 @@
       <c r="E96" s="10">
         <v>135</v>
       </c>
-      <c r="F96" s="11" t="s">
-        <v>14</v>
+      <c r="F96" s="9" t="s">
+        <v>6</v>
       </c>
       <c r="G96" s="4" t="s">
         <v>21</v>
@@ -2595,8 +2595,8 @@
         <f t="shared" si="1"/>
         <v>17.5</v>
       </c>
-      <c r="F98" s="11" t="s">
-        <v>14</v>
+      <c r="F98" s="9" t="s">
+        <v>6</v>
       </c>
       <c r="G98" s="4" t="s">
         <v>23</v>

--- a/Work.xlsx
+++ b/Work.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding\_print-hub\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spectre\Local Volume (D)\coding\_print-hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13BAA03E-BAF5-4965-80ED-AF0017BC9753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F930CA-45C2-45AE-A847-E4170A8BAEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="28">
   <si>
     <t>Date</t>
   </si>
@@ -115,6 +115,9 @@
   </si>
   <si>
     <t>Yusuf</t>
+  </si>
+  <si>
+    <t>Zainab</t>
   </si>
 </sst>
 </file>
@@ -201,10 +204,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -245,8 +249,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -586,7 +594,7 @@
       </c>
       <c r="I2" s="10">
         <f>SUM(E3:E1000)*0.9</f>
-        <v>5447.25</v>
+        <v>5845.5</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2603,81 +2611,276 @@
       </c>
     </row>
     <row r="99" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="12">
+        <v>46218</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D99" s="10">
+        <v>7</v>
+      </c>
       <c r="E99" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17.5</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="100" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="12">
+        <v>46218</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D100" s="10">
+        <v>16</v>
+      </c>
       <c r="E100" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="101" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="12">
+        <v>46218</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D101" s="10">
+        <v>50</v>
+      </c>
       <c r="E101" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>125</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="102" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="12">
+        <v>46218</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D102" s="10">
+        <v>2</v>
+      </c>
       <c r="E102" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="F102" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G102" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="103" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B103" s="12">
+        <v>46218</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D103" s="10">
+        <v>2</v>
+      </c>
       <c r="E103" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="F103" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="104" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B104" s="12">
+        <v>46218</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D104" s="10">
+        <v>2</v>
+      </c>
       <c r="E104" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="F104" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="105" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B105" s="12">
+        <v>46218</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D105" s="10">
+        <v>2</v>
+      </c>
       <c r="E105" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" ref="E105" si="2">D105*2.5</f>
+        <v>5</v>
+      </c>
+      <c r="F105" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="106" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B106" s="12">
+        <v>46219</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D106" s="10">
+        <v>10</v>
+      </c>
       <c r="E106" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="F106" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="107" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B107" s="12">
+        <v>46225</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D107" s="10">
+        <v>13</v>
+      </c>
       <c r="E107" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>32.5</v>
+      </c>
+      <c r="F107" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="108" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B108" s="12">
+        <v>46225</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D108" s="10">
+        <v>26</v>
+      </c>
       <c r="E108" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>65</v>
+      </c>
+      <c r="F108" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="109" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B109" s="12">
+        <v>46225</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D109" s="10">
+        <v>21</v>
+      </c>
       <c r="E109" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>52.5</v>
+      </c>
+      <c r="F109" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="110" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B110" s="12">
+        <v>46226</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D110" s="10">
+        <v>13</v>
+      </c>
       <c r="E110" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>32.5</v>
+      </c>
+      <c r="F110" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B111" s="12">
+        <v>46226</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D111" s="10">
+        <v>13</v>
+      </c>
       <c r="E111" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>32.5</v>
+      </c>
+      <c r="F111" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="112" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">

--- a/Work.xlsx
+++ b/Work.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spectre\Local Volume (D)\coding\_print-hub\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding\print-hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F930CA-45C2-45AE-A847-E4170A8BAEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB529A1-A878-4A9C-A77F-903D4979C39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="35">
   <si>
     <t>Date</t>
   </si>
@@ -118,6 +118,27 @@
   </si>
   <si>
     <t>Zainab</t>
+  </si>
+  <si>
+    <t>Rasil</t>
+  </si>
+  <si>
+    <t>Rifa</t>
+  </si>
+  <si>
+    <t>Yashfeen</t>
+  </si>
+  <si>
+    <t>Ravisha</t>
+  </si>
+  <si>
+    <t>Ayesha</t>
+  </si>
+  <si>
+    <t>Tanushree</t>
+  </si>
+  <si>
+    <t>Aiman</t>
   </si>
 </sst>
 </file>
@@ -208,7 +229,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -250,6 +271,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -558,7 +582,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="B1:I129"/>
+  <dimension ref="B1:I163"/>
   <sheetFormatPr defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -594,7 +618,7 @@
       </c>
       <c r="I2" s="10">
         <f>SUM(E3:E1000)*0.9</f>
-        <v>5845.5</v>
+        <v>6810.75</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2225,7 +2249,7 @@
         <v>86</v>
       </c>
       <c r="E80" s="10">
-        <f t="shared" ref="E80:E129" si="1">D80*2.5</f>
+        <f t="shared" ref="E80:E143" si="1">D80*2.5</f>
         <v>215</v>
       </c>
       <c r="F80" s="9" t="s">
@@ -2687,8 +2711,8 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F102" s="14" t="s">
-        <v>14</v>
+      <c r="F102" s="9" t="s">
+        <v>6</v>
       </c>
       <c r="G102" s="4" t="s">
         <v>23</v>
@@ -2708,8 +2732,8 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F103" s="14" t="s">
-        <v>14</v>
+      <c r="F103" s="9" t="s">
+        <v>6</v>
       </c>
       <c r="G103" s="4" t="s">
         <v>23</v>
@@ -2729,8 +2753,8 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F104" s="14" t="s">
-        <v>14</v>
+      <c r="F104" s="9" t="s">
+        <v>6</v>
       </c>
       <c r="G104" s="4" t="s">
         <v>23</v>
@@ -2750,8 +2774,8 @@
         <f t="shared" ref="E105" si="2">D105*2.5</f>
         <v>5</v>
       </c>
-      <c r="F105" s="14" t="s">
-        <v>14</v>
+      <c r="F105" s="9" t="s">
+        <v>6</v>
       </c>
       <c r="G105" s="4" t="s">
         <v>23</v>
@@ -2813,8 +2837,8 @@
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
-      <c r="F108" s="14" t="s">
-        <v>14</v>
+      <c r="F108" s="9" t="s">
+        <v>6</v>
       </c>
       <c r="G108" s="4" t="s">
         <v>23</v>
@@ -2834,8 +2858,8 @@
         <f t="shared" si="1"/>
         <v>52.5</v>
       </c>
-      <c r="F109" s="14" t="s">
-        <v>14</v>
+      <c r="F109" s="9" t="s">
+        <v>6</v>
       </c>
       <c r="G109" s="4" t="s">
         <v>23</v>
@@ -2855,8 +2879,8 @@
         <f t="shared" si="1"/>
         <v>32.5</v>
       </c>
-      <c r="F110" s="14" t="s">
-        <v>14</v>
+      <c r="F110" s="9" t="s">
+        <v>6</v>
       </c>
       <c r="G110" s="4" t="s">
         <v>23</v>
@@ -2876,120 +2900,834 @@
         <f t="shared" si="1"/>
         <v>32.5</v>
       </c>
-      <c r="F111" s="14" t="s">
+      <c r="F111" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="112" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B112" s="12">
+        <v>46226</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D112" s="15">
+        <v>16</v>
+      </c>
+      <c r="E112" s="10">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="F112" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="113" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B113" s="12">
+        <v>46231</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D113" s="15">
+        <v>13</v>
+      </c>
+      <c r="E113" s="10">
+        <f t="shared" si="1"/>
+        <v>32.5</v>
+      </c>
+      <c r="F113" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="114" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B114" s="12">
+        <v>46231</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D114" s="15">
+        <v>16</v>
+      </c>
+      <c r="E114" s="10">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="F114" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="115" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B115" s="12">
+        <v>46232</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D115" s="15">
+        <v>6</v>
+      </c>
+      <c r="E115" s="10">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="F115" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="G111" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="112" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E112" s="10">
-        <f t="shared" si="1"/>
+      <c r="G115" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="116" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B116" s="12">
+        <v>46233</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D116" s="15">
+        <v>11</v>
+      </c>
+      <c r="E116" s="10">
+        <f t="shared" si="1"/>
+        <v>27.5</v>
+      </c>
+      <c r="F116" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G116" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="117" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B117" s="12">
+        <v>46233</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D117" s="15">
+        <v>17</v>
+      </c>
+      <c r="E117" s="10">
+        <f t="shared" si="1"/>
+        <v>42.5</v>
+      </c>
+      <c r="F117" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="118" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B118" s="12">
+        <v>46233</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D118" s="15">
+        <v>11</v>
+      </c>
+      <c r="E118" s="10">
+        <f t="shared" si="1"/>
+        <v>27.5</v>
+      </c>
+      <c r="F118" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G118" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="119" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B119" s="12">
+        <v>46233</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D119" s="15">
+        <v>26</v>
+      </c>
+      <c r="E119" s="10">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="F119" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G119" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="120" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B120" s="12">
+        <v>46233</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D120" s="15">
+        <v>2</v>
+      </c>
+      <c r="E120" s="10">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="F120" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G120" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="121" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B121" s="12">
+        <v>46239</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D121" s="15">
+        <v>20</v>
+      </c>
+      <c r="E121" s="10">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="F121" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G121" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="122" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B122" s="12">
+        <v>46240</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D122" s="15">
+        <v>7</v>
+      </c>
+      <c r="E122" s="10">
+        <f t="shared" si="1"/>
+        <v>17.5</v>
+      </c>
+      <c r="F122" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G122" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="123" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B123" s="12">
+        <v>46240</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D123" s="15">
+        <v>11</v>
+      </c>
+      <c r="E123" s="10">
+        <f t="shared" si="1"/>
+        <v>27.5</v>
+      </c>
+      <c r="F123" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="124" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B124" s="12">
+        <v>46240</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D124" s="15">
+        <v>24</v>
+      </c>
+      <c r="E124" s="10">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="F124" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G124" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="125" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B125" s="12">
+        <v>46240</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D125" s="15">
+        <v>4</v>
+      </c>
+      <c r="E125" s="10">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="F125" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G125" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="126" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B126" s="12">
+        <v>46240</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D126" s="15">
+        <v>6</v>
+      </c>
+      <c r="E126" s="10">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="F126" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G126" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="127" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B127" s="12">
+        <v>46240</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D127" s="15">
+        <v>10</v>
+      </c>
+      <c r="E127" s="10">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="F127" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G127" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="128" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B128" s="12">
+        <v>46240</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D128" s="15">
+        <v>12</v>
+      </c>
+      <c r="E128" s="10">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F128" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G128" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="129" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B129" s="12">
+        <v>46240</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D129" s="15">
+        <v>19</v>
+      </c>
+      <c r="E129" s="10">
+        <f t="shared" si="1"/>
+        <v>47.5</v>
+      </c>
+      <c r="F129" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G129" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="130" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B130" s="12">
+        <v>46241</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D130" s="15">
+        <v>34</v>
+      </c>
+      <c r="E130" s="10">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+      <c r="F130" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G130" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="131" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B131" s="12">
+        <v>46241</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D131" s="15">
+        <v>21</v>
+      </c>
+      <c r="E131" s="10">
+        <f t="shared" si="1"/>
+        <v>52.5</v>
+      </c>
+      <c r="F131" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G131" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="132" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B132" s="12">
+        <v>46241</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D132" s="15">
+        <v>26</v>
+      </c>
+      <c r="E132" s="10">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="F132" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G132" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="133" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B133" s="12">
+        <v>46241</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D133" s="15">
+        <v>4</v>
+      </c>
+      <c r="E133" s="10">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="F133" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G133" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="134" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B134" s="12">
+        <v>46246</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D134" s="15">
+        <v>13</v>
+      </c>
+      <c r="E134" s="10">
+        <f t="shared" si="1"/>
+        <v>32.5</v>
+      </c>
+      <c r="F134" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G134" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="135" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B135" s="12">
+        <v>46246</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D135" s="15">
+        <v>12</v>
+      </c>
+      <c r="E135" s="10">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F135" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G135" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="136" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B136" s="12">
+        <v>46246</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D136" s="15">
+        <v>2</v>
+      </c>
+      <c r="E136" s="10">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="F136" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G136" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="137" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B137" s="12">
+        <v>46246</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D137" s="15">
+        <v>1</v>
+      </c>
+      <c r="E137" s="10">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+      <c r="F137" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G137" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="138" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B138" s="12">
+        <v>46246</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D138" s="15">
+        <v>13</v>
+      </c>
+      <c r="E138" s="10">
+        <f t="shared" si="1"/>
+        <v>32.5</v>
+      </c>
+      <c r="F138" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G138" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="139" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B139" s="12">
+        <v>46246</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D139" s="15">
+        <v>1</v>
+      </c>
+      <c r="E139" s="10">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+      <c r="F139" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G139" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="140" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B140" s="12">
+        <v>46248</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D140" s="4">
+        <v>17</v>
+      </c>
+      <c r="E140" s="10">
+        <f t="shared" si="1"/>
+        <v>42.5</v>
+      </c>
+      <c r="F140" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G140" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="141" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B141" s="12">
+        <v>46248</v>
+      </c>
+      <c r="C141" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D141" s="4">
+        <v>20</v>
+      </c>
+      <c r="E141" s="10">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="F141" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G141" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="142" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B142" s="12">
+        <v>46248</v>
+      </c>
+      <c r="C142" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D142" s="4">
+        <v>30</v>
+      </c>
+      <c r="E142" s="10">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="F142" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G142" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="143" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B143" s="12">
+        <v>46250</v>
+      </c>
+      <c r="C143" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D143" s="4">
+        <v>2</v>
+      </c>
+      <c r="E143" s="10">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="F143" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G143" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="144" spans="2:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B144" s="12">
+        <v>46250</v>
+      </c>
+      <c r="C144" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D144" s="4">
+        <v>2</v>
+      </c>
+      <c r="E144" s="10">
+        <f t="shared" ref="E144:E161" si="3">D144*2.5</f>
+        <v>5</v>
+      </c>
+      <c r="F144" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G144" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="145" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C145" s="10"/>
+      <c r="D145" s="4"/>
+      <c r="E145" s="10">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E113" s="10">
-        <f t="shared" si="1"/>
+    <row r="146" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C146" s="10"/>
+      <c r="D146" s="4"/>
+      <c r="E146" s="10">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E114" s="10">
-        <f t="shared" si="1"/>
+    <row r="147" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C147" s="10"/>
+      <c r="D147" s="4"/>
+      <c r="E147" s="10">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E115" s="10">
-        <f t="shared" si="1"/>
+    <row r="148" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C148" s="10"/>
+      <c r="D148" s="4"/>
+      <c r="E148" s="10">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E116" s="10">
-        <f t="shared" si="1"/>
+    <row r="149" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D149" s="4"/>
+      <c r="E149" s="10">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E117" s="10">
-        <f t="shared" si="1"/>
+    <row r="150" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D150" s="4"/>
+      <c r="E150" s="10">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E118" s="10">
-        <f t="shared" si="1"/>
+    <row r="151" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D151" s="4"/>
+      <c r="E151" s="10">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E119" s="10">
-        <f t="shared" si="1"/>
+    <row r="152" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D152" s="4"/>
+      <c r="E152" s="10">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E120" s="10">
-        <f t="shared" si="1"/>
+    <row r="153" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D153" s="4"/>
+      <c r="E153" s="10">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E121" s="10">
-        <f t="shared" si="1"/>
+    <row r="154" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D154" s="4"/>
+      <c r="E154" s="10">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E122" s="10">
-        <f t="shared" si="1"/>
+    <row r="155" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D155" s="4"/>
+      <c r="E155" s="10">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E123" s="10">
-        <f t="shared" si="1"/>
+    <row r="156" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D156" s="4"/>
+      <c r="E156" s="10">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E124" s="10">
-        <f t="shared" si="1"/>
+    <row r="157" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D157" s="4"/>
+      <c r="E157" s="10">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E125" s="10">
-        <f t="shared" si="1"/>
+    <row r="158" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D158" s="4"/>
+      <c r="E158" s="10">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E126" s="10">
-        <f t="shared" si="1"/>
+    <row r="159" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D159" s="4"/>
+      <c r="E159" s="10">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E127" s="10">
-        <f t="shared" si="1"/>
+    <row r="160" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D160" s="4"/>
+      <c r="E160" s="10">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E128" s="10">
-        <f t="shared" si="1"/>
+    <row r="161" spans="4:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D161" s="4"/>
+      <c r="E161" s="10">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="5:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E129" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="162" spans="4:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D162" s="4"/>
+    </row>
+    <row r="163" spans="4:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D163" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
